--- a/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 1,18</t>
+          <t>-8,15; 1,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,74</t>
+          <t>-5,12; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 13,33</t>
+          <t>0,37; 12,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 1,31</t>
+          <t>-9,3; 1,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,57</t>
+          <t>-6,49; 5,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,13</t>
+          <t>-2,97; 7,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,15</t>
+          <t>-6,99; 0,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,86</t>
+          <t>-4,29; 4,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,23</t>
+          <t>0,64; 8,91</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 14,15</t>
+          <t>-57,07; 25,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 72,01</t>
+          <t>-37,15; 73,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 153,42</t>
+          <t>2,29; 154,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 15,17</t>
+          <t>-57,77; 20,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 56,26</t>
+          <t>-40,46; 57,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 72,16</t>
+          <t>-17,7; 78,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 1,85</t>
+          <t>-50,1; 4,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 39,31</t>
+          <t>-31,39; 39,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 93,59</t>
+          <t>3,99; 89,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,69</t>
+          <t>-5,32; 1,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,33</t>
+          <t>-2,45; 4,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,82</t>
+          <t>3,89; 12,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,24</t>
+          <t>-5,81; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,98</t>
+          <t>-5,4; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 11,42</t>
+          <t>3,42; 11,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,23</t>
+          <t>-4,39; 0,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,92</t>
+          <t>-3,11; 2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,94</t>
+          <t>5,0; 11,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 41,57</t>
+          <t>-60,01; 35,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 79,21</t>
+          <t>-28,73; 94,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,39; 224,63</t>
+          <t>43,48; 248,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 16,52</t>
+          <t>-51,82; 13,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 26,46</t>
+          <t>-47,09; 24,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,32; 151,46</t>
+          <t>28,3; 147,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 3,35</t>
+          <t>-46,5; 4,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 27,08</t>
+          <t>-32,37; 30,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,43; 157,48</t>
+          <t>50,24; 159,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,06</t>
+          <t>-3,62; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,38</t>
+          <t>-1,86; 6,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 17,47</t>
+          <t>6,29; 16,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 10,24</t>
+          <t>-0,2; 9,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,88</t>
+          <t>0,62; 10,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 17,55</t>
+          <t>7,9; 17,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 6,24</t>
+          <t>-0,38; 6,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,92</t>
+          <t>0,26; 6,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,83</t>
+          <t>8,98; 15,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 110,64</t>
+          <t>-39,62; 87,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 130,42</t>
+          <t>-23,58; 121,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,67; 361,35</t>
+          <t>60,91; 337,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 157,56</t>
+          <t>-3,32; 145,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 147,15</t>
+          <t>2,89; 160,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,39; 280,09</t>
+          <t>65,28; 271,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 97,99</t>
+          <t>-5,49; 97,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 105,39</t>
+          <t>0,82; 105,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92,22; 260,96</t>
+          <t>89,97; 241,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 7,91</t>
+          <t>0,28; 8,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,53</t>
+          <t>1,75; 9,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 23,13</t>
+          <t>10,23; 22,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,46</t>
+          <t>-5,11; 2,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,53</t>
+          <t>-0,9; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 13,1</t>
+          <t>0,13; 13,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,39</t>
+          <t>-1,47; 4,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,95</t>
+          <t>1,5; 8,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,37</t>
+          <t>5,66; 15,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 193,42</t>
+          <t>-0,37; 213,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,6; 245,67</t>
+          <t>19,94; 255,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125,37; 590,04</t>
+          <t>130,59; 531,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 47,09</t>
+          <t>-43,15; 38,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 108,26</t>
+          <t>-11,39; 106,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 164,46</t>
+          <t>1,47; 160,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 69,35</t>
+          <t>-16,76; 70,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,69; 125,73</t>
+          <t>13,08; 115,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,18; 230,72</t>
+          <t>71,92; 232,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 0,61</t>
+          <t>-9,52; 0,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 11,32</t>
+          <t>-1,5; 11,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,91; 22,09</t>
+          <t>8,18; 22,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,4</t>
+          <t>-1,18; 7,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 9,85</t>
+          <t>0,21; 10,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 17,8</t>
+          <t>4,41; 17,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,8</t>
+          <t>-3,85; 2,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,9</t>
+          <t>0,78; 8,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,54</t>
+          <t>6,37; 17,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,39; 14,42</t>
+          <t>-76,28; 12,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 170,02</t>
+          <t>-12,6; 176,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64,13; 344,52</t>
+          <t>60,24; 335,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 384,59</t>
+          <t>-22,18; 381,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,43; 438,97</t>
+          <t>-4,36; 468,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,83; 843,05</t>
+          <t>79,33; 782,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 60,16</t>
+          <t>-48,44; 53,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,72; 181,81</t>
+          <t>7,58; 181,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74,92; 347,62</t>
+          <t>95,25; 345,12</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,11</t>
+          <t>-5,01; 4,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 8,49</t>
+          <t>-1,55; 9,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,1; 24,7</t>
+          <t>13,21; 24,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 7,77</t>
+          <t>-3,84; 7,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 7,91</t>
+          <t>-3,37; 7,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,69</t>
+          <t>3,73; 14,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,61</t>
+          <t>-2,93; 4,31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,14</t>
+          <t>-1,61; 6,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10,69; 17,87</t>
+          <t>10,04; 18,05</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 70,04</t>
+          <t>-49,08; 84,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 145,65</t>
+          <t>-20,1; 171,59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115,39; 429,53</t>
+          <t>121,81; 430,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 90,84</t>
+          <t>-27,17; 87,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 91,03</t>
+          <t>-25,17; 95,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,1; 177,62</t>
+          <t>24,39; 168,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 59,25</t>
+          <t>-26,01; 54,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 75,3</t>
+          <t>-14,71; 77,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82,69; 223,34</t>
+          <t>85,19; 236,14</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,58</t>
+          <t>-0,82; 5,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,87; 15,68</t>
+          <t>7,38; 15,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,71; 14,37</t>
+          <t>6,62; 14,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,1</t>
+          <t>-0,41; 6,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,28</t>
+          <t>7,85; 15,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,32</t>
+          <t>-4,19; 6,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,08</t>
+          <t>0,01; 4,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>8,86; 14,47</t>
+          <t>8,69; 14,11</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,64</t>
+          <t>0,35; 9,03</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 102,01</t>
+          <t>-12,19; 100,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>90,3; 288,14</t>
+          <t>82,11; 289,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>75,18; 258,99</t>
+          <t>76,56; 261,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 89,34</t>
+          <t>-6,53; 93,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>80,84; 232,55</t>
+          <t>77,55; 227,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 83,98</t>
+          <t>-40,59; 81,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,28; 74,97</t>
+          <t>0,15; 74,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>97,87; 221,66</t>
+          <t>94,28; 210,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,66; 125,57</t>
+          <t>5,13; 129,21</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,31</t>
+          <t>1,4; 7,43</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,49</t>
+          <t>3,36; 9,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,19</t>
+          <t>-2,23; 8,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,41</t>
+          <t>-0,55; 5,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,77</t>
+          <t>1,65; 7,97</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,85</t>
+          <t>8,37; 14,39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,24</t>
+          <t>1,4; 5,26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,79</t>
+          <t>3,41; 7,77</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 10,09</t>
+          <t>1,38; 10,16</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,89; 143,69</t>
+          <t>19,24; 156,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>48,43; 192,37</t>
+          <t>44,21; 203,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 146,73</t>
+          <t>-28,1; 154,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 91,38</t>
+          <t>-5,86; 86,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,05; 128,61</t>
+          <t>21,62; 139,02</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>88,41; 240,85</t>
+          <t>93,09; 242,35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,43; 86,3</t>
+          <t>17,12; 90,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>44,59; 130,93</t>
+          <t>42,36; 131,01</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26,19; 164,22</t>
+          <t>30,82; 163,06</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,47</t>
+          <t>-0,31; 2,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,94</t>
+          <t>3,6; 6,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,56</t>
+          <t>5,65; 11,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,59</t>
+          <t>-0,2; 2,8</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,0</t>
+          <t>2,95; 6,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,3</t>
+          <t>4,24; 9,26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,06</t>
+          <t>0,14; 2,17</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,85</t>
+          <t>3,78; 5,89</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,98</t>
+          <t>6,23; 9,87</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 36,48</t>
+          <t>-3,77; 37,87</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>47,33; 102,2</t>
+          <t>43,69; 99,09</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>74,99; 171,77</t>
+          <t>77,09; 173,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 32,41</t>
+          <t>-2,34; 33,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>30,85; 75,35</t>
+          <t>32,11; 76,08</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>46,84; 112,7</t>
+          <t>49,65; 113,27</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,53; 26,89</t>
+          <t>1,68; 28,73</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>44,27; 77,23</t>
+          <t>44,08; 77,76</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>74,99; 130,52</t>
+          <t>75,34; 128,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,74</t>
+          <t>-8,67; 1,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 6,13</t>
+          <t>-5,21; 5,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 12,95</t>
+          <t>1,25; 13,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 1,67</t>
+          <t>-9,41; 1,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 5,44</t>
+          <t>-5,93; 5,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,54</t>
+          <t>-3,7; 7,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,44</t>
+          <t>-7,37; 0,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,09</t>
+          <t>-4,3; 3,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,91</t>
+          <t>0,31; 8,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,07; 25,75</t>
+          <t>-59,74; 13,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 73,85</t>
+          <t>-38,66; 62,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 154,25</t>
+          <t>7,29; 150,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 20,37</t>
+          <t>-60,52; 14,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 57,43</t>
+          <t>-39,02; 52,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 78,21</t>
+          <t>-21,73; 77,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 4,81</t>
+          <t>-51,93; 1,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 39,86</t>
+          <t>-30,11; 37,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 89,49</t>
+          <t>2,01; 79,7</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,62</t>
+          <t>-5,63; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,74</t>
+          <t>-2,42; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,98</t>
+          <t>4,32; 13,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,97</t>
+          <t>-5,61; 1,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,56</t>
+          <t>-5,48; 1,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,2</t>
+          <t>3,33; 10,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,35</t>
+          <t>-4,65; 0,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,07</t>
+          <t>-2,97; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,24</t>
+          <t>4,91; 10,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115,5%</t>
+          <t>121,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 35,03</t>
+          <t>-61,15; 27,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 94,35</t>
+          <t>-27,87; 81,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,48; 248,74</t>
+          <t>46,91; 250,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 13,36</t>
+          <t>-50,17; 19,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,09; 24,65</t>
+          <t>-47,37; 23,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,3; 147,16</t>
+          <t>28,18; 149,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 4,98</t>
+          <t>-47,21; 2,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 30,62</t>
+          <t>-31,08; 29,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,24; 159,2</t>
+          <t>50,04; 151,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,89</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,71</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,34</t>
+          <t>12,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,72</t>
+          <t>-3,56; 5,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,59</t>
+          <t>-1,57; 6,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 16,96</t>
+          <t>7,21; 17,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 9,73</t>
+          <t>-0,02; 10,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,53</t>
+          <t>0,4; 10,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 17,41</t>
+          <t>8,13; 17,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,18</t>
+          <t>-0,27; 6,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,79</t>
+          <t>0,48; 7,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 15,49</t>
+          <t>9,25; 15,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169,92%</t>
+          <t>175,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>144,52%</t>
+          <t>141,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>155,86%</t>
+          <t>156,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 87,81</t>
+          <t>-39,64; 110,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 121,33</t>
+          <t>-20,97; 142,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,91; 337,22</t>
+          <t>67,84; 335,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 145,93</t>
+          <t>-1,87; 157,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 160,76</t>
+          <t>2,93; 156,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,28; 271,44</t>
+          <t>64,05; 265,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 97,14</t>
+          <t>-4,01; 91,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 105,99</t>
+          <t>3,6; 107,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89,97; 241,88</t>
+          <t>91,33; 244,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,96</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>14,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 8,42</t>
+          <t>0,2; 8,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,91</t>
+          <t>1,6; 9,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,23; 22,04</t>
+          <t>11,06; 23,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,86</t>
+          <t>-4,99; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 8,49</t>
+          <t>-0,89; 8,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 13,14</t>
+          <t>7,21; 15,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,45</t>
+          <t>-1,13; 4,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,01</t>
+          <t>1,6; 8,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 15,26</t>
+          <t>10,51; 17,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>283,27%</t>
+          <t>301,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>116,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>144,09%</t>
+          <t>181,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 213,07</t>
+          <t>-0,76; 211,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,94; 255,82</t>
+          <t>18,21; 249,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130,59; 531,69</t>
+          <t>144,04; 616,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 38,0</t>
+          <t>-42,41; 42,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 106,51</t>
+          <t>-9,15; 105,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 160,28</t>
+          <t>60,15; 221,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 70,98</t>
+          <t>-13,71; 76,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 115,61</t>
+          <t>16,58; 127,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,92; 232,17</t>
+          <t>113,24; 283,67</t>
         </is>
       </c>
     </row>
@@ -1498,24 +1498,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>15,34</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5,02</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>15,28</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,02</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>15,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 0,63</t>
+          <t>-9,79; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 11,34</t>
+          <t>-0,53; 12,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 22,12</t>
+          <t>8,66; 22,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 7,82</t>
+          <t>-0,51; 7,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,06</t>
+          <t>0,31; 10,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,41; 17,79</t>
+          <t>10,81; 19,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,7</t>
+          <t>-4,39; 2,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,76</t>
+          <t>1,08; 9,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 17,46</t>
+          <t>11,49; 19,52</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161,67%</t>
+          <t>162,26%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>308,78%</t>
+          <t>392,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>193,78%</t>
+          <t>228,59%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,28; 12,48</t>
+          <t>-77,37; 12,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 176,41</t>
+          <t>-8,53; 182,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60,24; 335,87</t>
+          <t>67,35; 347,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 381,1</t>
+          <t>-15,9; 371,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 468,7</t>
+          <t>-3,47; 468,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,33; 782,09</t>
+          <t>142,61; 970,89</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 53,82</t>
+          <t>-51,03; 55,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,58; 181,93</t>
+          <t>11,02; 191,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>95,25; 345,12</t>
+          <t>124,01; 397,77</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18,77</t>
+          <t>19,12</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>14,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 4,6</t>
+          <t>-4,97; 4,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 9,24</t>
+          <t>-1,74; 8,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,21; 24,59</t>
+          <t>13,86; 24,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,22</t>
+          <t>-3,59; 7,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,75</t>
+          <t>-3,57; 6,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,73; 14,33</t>
+          <t>4,02; 14,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,31</t>
+          <t>-2,81; 4,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,27</t>
+          <t>-1,36; 6,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10,04; 18,05</t>
+          <t>10,8; 18,66</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231,37%</t>
+          <t>235,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>146,26%</t>
+          <t>149,92%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 84,39</t>
+          <t>-50,57; 71,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 171,59</t>
+          <t>-18,85; 136,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>121,81; 430,94</t>
+          <t>128,89; 453,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 87,25</t>
+          <t>-27,45; 83,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 95,91</t>
+          <t>-26,52; 77,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,39; 168,87</t>
+          <t>26,32; 178,43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 54,86</t>
+          <t>-24,68; 51,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 77,64</t>
+          <t>-11,73; 79,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>85,19; 236,14</t>
+          <t>90,88; 238,69</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,41</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>8,04</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,6</t>
+          <t>-1,17; 5,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,81</t>
+          <t>7,51; 15,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,26</t>
+          <t>6,83; 14,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,32</t>
+          <t>-0,38; 6,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,85; 15,52</t>
+          <t>7,98; 15,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 6,27</t>
+          <t>2,23; 8,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,82</t>
+          <t>0,13; 4,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,11</t>
+          <t>8,87; 14,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 9,03</t>
+          <t>5,68; 10,47</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>146,81%</t>
+          <t>153,96%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>104,2%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 100,03</t>
+          <t>-14,36; 95,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>82,11; 289,25</t>
+          <t>83,97; 275,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>76,56; 261,51</t>
+          <t>77,65; 252,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 93,24</t>
+          <t>-3,92; 89,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>77,55; 227,54</t>
+          <t>77,52; 247,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 81,35</t>
+          <t>19,45; 124,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,15; 74,3</t>
+          <t>1,17; 71,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>94,28; 210,08</t>
+          <t>98,86; 211,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,13; 129,21</t>
+          <t>62,58; 158,96</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>9,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,43</t>
+          <t>1,48; 7,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,52</t>
+          <t>3,63; 9,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 8,49</t>
+          <t>4,52; 10,42</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,09</t>
+          <t>-0,5; 5,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,97</t>
+          <t>1,94; 8,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,37; 14,39</t>
+          <t>8,06; 14,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,26</t>
+          <t>1,3; 5,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,77</t>
+          <t>3,49; 7,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,16</t>
+          <t>7,19; 11,45</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>125,44%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>150,95%</t>
+          <t>147,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>101,98%</t>
+          <t>137,84%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,24; 156,72</t>
+          <t>20,24; 149,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>44,21; 203,35</t>
+          <t>44,74; 186,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 154,84</t>
+          <t>63,53; 219,42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 86,5</t>
+          <t>-6,24; 85,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>21,62; 139,02</t>
+          <t>20,63; 132,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>93,09; 242,35</t>
+          <t>91,02; 235,2</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,12; 90,43</t>
+          <t>16,04; 91,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>42,36; 131,01</t>
+          <t>44,53; 127,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>30,82; 163,06</t>
+          <t>95,16; 198,38</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>9,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,54</t>
+          <t>-0,24; 2,48</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,66</t>
+          <t>3,81; 6,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,61</t>
+          <t>9,58; 12,84</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,8</t>
+          <t>-0,2; 2,7</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,03</t>
+          <t>2,98; 5,98</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,26</t>
+          <t>7,38; 10,18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,17</t>
+          <t>0,16; 2,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,89</t>
+          <t>3,7; 6,01</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,87</t>
+          <t>8,86; 10,98</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>129,92%</t>
+          <t>152,99%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>100,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>105,1%</t>
+          <t>124,02%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 37,87</t>
+          <t>-3,37; 37,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>43,69; 99,09</t>
+          <t>47,44; 103,41</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>77,09; 173,62</t>
+          <t>120,91; 200,07</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 33,83</t>
+          <t>-2,48; 33,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>32,11; 76,08</t>
+          <t>31,07; 74,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>49,65; 113,27</t>
+          <t>77,37; 127,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,68; 28,73</t>
+          <t>1,79; 28,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>44,08; 77,76</t>
+          <t>42,87; 79,5</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>75,34; 128,64</t>
+          <t>103,32; 145,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
